--- a/output_plant/stomata_Intermediate_sun_2012.xlsx
+++ b/output_plant/stomata_Intermediate_sun_2012.xlsx
@@ -606,7 +606,7 @@
     <t xml:space="preserve">10.3906/yer-1003-42</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/stomata-sr_sun_2012.xlsx</t>
+    <t xml:space="preserve">stomata-sr_sun_2012_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>

--- a/output_plant/stomata_Intermediate_sun_2012.xlsx
+++ b/output_plant/stomata_Intermediate_sun_2012.xlsx
@@ -615,7 +615,7 @@
     <t xml:space="preserve">dustin.t.harper@utah.edu; claudiag@ldeo.columbia.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">Bounded by two radiometric dates of 3.297 +/- 0.040 Ma and 2.322 +/- 0.036 Ma; fossils come from a 42 m thick section, which is estimated based on sedimentation rates to represent ~0.47 Myrs. From these arguments, the authors argue for a "Late Pliocene age (3.30-2.83 Ma). Following GTS 2020 and the older radiometric constraint, the "Late Pliocene" (Piacenzian) spans 3.297 - 2.59 Ma.</t>
+    <t xml:space="preserve">Bounded by two radiometric dates of 3.297 +/- 0.040 Ma and 2.322 +/- 0.036 Ma; fossils come from a 42 m thick section, which is estimated based on sedimentation rates to represent ~0.47 Myrs. From these arguments, the authors argue for a "Late Pliocene age (3.30-2.83 Ma). Following GTS 2020 and the older radiometric constraint, the "Late Pliocene" (Piacenzian) spans 3.297 - 2.59 Ma.; Age updated to GTS 2020</t>
   </si>
   <si>
     <t xml:space="preserve">Betulaceae / Betula</t>
